--- a/data.mn/public/datasets/university-graduates-by-field.xlsx
+++ b/data.mn/public/datasets/university-graduates-by-field.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,41 @@
         <v>1424</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B8" t="n">
+        <v>304</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7579</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4116</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3481</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6269</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1354</v>
+      </c>
+      <c r="I8" t="n">
+        <v>499</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1132</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1645</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -708,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -991,6 +1026,41 @@
         <v>1330</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B8" t="n">
+        <v>499</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7579</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4116</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3481</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1354</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1645</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1996</v>
+      </c>
+      <c r="I8" t="n">
+        <v>304</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6269</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
